--- a/artfynd/A 11288-2024 artfynd.xlsx
+++ b/artfynd/A 11288-2024 artfynd.xlsx
@@ -1214,12 +1214,7 @@
         <v>116929266</v>
       </c>
       <c r="B7" t="n">
-        <v>57299</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57653</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1252,7 +1247,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Holmensbäcken (Holmensbäcken), Mpd</t>
+          <t>Holmensbäcken, Holmensbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -1321,12 +1316,7 @@
         <v>116930260</v>
       </c>
       <c r="B8" t="n">
-        <v>57294</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,7 +1344,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Holmensbäcken (Holmensbäcken), Mpd</t>
+          <t>Holmensbäcken, Holmensbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">

--- a/artfynd/A 11288-2024 artfynd.xlsx
+++ b/artfynd/A 11288-2024 artfynd.xlsx
@@ -1214,7 +1214,7 @@
         <v>116929266</v>
       </c>
       <c r="B7" t="n">
-        <v>57653</v>
+        <v>57655</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>116930260</v>
       </c>
       <c r="B8" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 11288-2024 artfynd.xlsx
+++ b/artfynd/A 11288-2024 artfynd.xlsx
@@ -1214,7 +1214,7 @@
         <v>116929266</v>
       </c>
       <c r="B7" t="n">
-        <v>57655</v>
+        <v>57658</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>116930260</v>
       </c>
       <c r="B8" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 11288-2024 artfynd.xlsx
+++ b/artfynd/A 11288-2024 artfynd.xlsx
@@ -1214,7 +1214,7 @@
         <v>116929266</v>
       </c>
       <c r="B7" t="n">
-        <v>57658</v>
+        <v>57664</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>116930260</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 11288-2024 artfynd.xlsx
+++ b/artfynd/A 11288-2024 artfynd.xlsx
@@ -1214,7 +1214,7 @@
         <v>116929266</v>
       </c>
       <c r="B7" t="n">
-        <v>57664</v>
+        <v>57665</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>116930260</v>
       </c>
       <c r="B8" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 11288-2024 artfynd.xlsx
+++ b/artfynd/A 11288-2024 artfynd.xlsx
@@ -1214,7 +1214,7 @@
         <v>116929266</v>
       </c>
       <c r="B7" t="n">
-        <v>57665</v>
+        <v>57676</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>116930260</v>
       </c>
       <c r="B8" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 11288-2024 artfynd.xlsx
+++ b/artfynd/A 11288-2024 artfynd.xlsx
@@ -1522,7 +1522,7 @@
         <v>131110722</v>
       </c>
       <c r="B10" t="n">
-        <v>80254</v>
+        <v>80255</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 11288-2024 artfynd.xlsx
+++ b/artfynd/A 11288-2024 artfynd.xlsx
@@ -1413,7 +1413,7 @@
         <v>131110701</v>
       </c>
       <c r="B9" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>131110722</v>
       </c>
       <c r="B10" t="n">
-        <v>80255</v>
+        <v>80257</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 11288-2024 artfynd.xlsx
+++ b/artfynd/A 11288-2024 artfynd.xlsx
@@ -1413,7 +1413,7 @@
         <v>131110701</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>131110722</v>
       </c>
       <c r="B10" t="n">
-        <v>80257</v>
+        <v>80258</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 11288-2024 artfynd.xlsx
+++ b/artfynd/A 11288-2024 artfynd.xlsx
@@ -1413,7 +1413,7 @@
         <v>131110701</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>131110722</v>
       </c>
       <c r="B10" t="n">
-        <v>80258</v>
+        <v>80259</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 11288-2024 artfynd.xlsx
+++ b/artfynd/A 11288-2024 artfynd.xlsx
@@ -1413,7 +1413,7 @@
         <v>131110701</v>
       </c>
       <c r="B9" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>131110722</v>
       </c>
       <c r="B10" t="n">
-        <v>80259</v>
+        <v>80262</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 11288-2024 artfynd.xlsx
+++ b/artfynd/A 11288-2024 artfynd.xlsx
@@ -1413,7 +1413,7 @@
         <v>131110701</v>
       </c>
       <c r="B9" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>131110722</v>
       </c>
       <c r="B10" t="n">
-        <v>80262</v>
+        <v>80263</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 11288-2024 artfynd.xlsx
+++ b/artfynd/A 11288-2024 artfynd.xlsx
@@ -1413,7 +1413,7 @@
         <v>131110701</v>
       </c>
       <c r="B9" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>131110722</v>
       </c>
       <c r="B10" t="n">
-        <v>80263</v>
+        <v>80269</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 11288-2024 artfynd.xlsx
+++ b/artfynd/A 11288-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>115639618</v>
       </c>
       <c r="B2" t="n">
-        <v>90343</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,7 +706,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Holmensbäcken (Holmensbäcken), Mpd</t>
+          <t>Holmensbäcken, Holmensbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115640666</v>
+        <v>115640415</v>
       </c>
       <c r="B3" t="n">
-        <v>90343</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,14 +803,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Holmensbäcken (Holmensbäcken), Mpd</t>
+          <t>Holmensbäcken, Holmensbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>631222</v>
+        <v>631085</v>
       </c>
       <c r="R3" t="n">
-        <v>6928057</v>
+        <v>6928002</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115640415</v>
+        <v>115640666</v>
       </c>
       <c r="B4" t="n">
-        <v>90343</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,14 +900,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Holmensbäcken (Holmensbäcken), Mpd</t>
+          <t>Holmensbäcken, Holmensbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631085</v>
+        <v>631222</v>
       </c>
       <c r="R4" t="n">
-        <v>6928002</v>
+        <v>6928057</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,12 +969,7 @@
         <v>115702027</v>
       </c>
       <c r="B5" t="n">
-        <v>90343</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1020,7 +1000,7 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Holmensbäcken (Holmensbäcken), Mpd</t>
+          <t>Holmensbäcken, Holmensbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1087,15 +1067,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115703646</v>
+        <v>131110722</v>
       </c>
       <c r="B6" t="n">
-        <v>56577</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,49 +1078,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100038</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Holmensbäcken (Holmensbäcken), Mpd</t>
+          <t>Myckeläng, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>631093</v>
+        <v>631117</v>
       </c>
       <c r="R6" t="n">
-        <v>6927953</v>
+        <v>6928040</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1169,22 +1135,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:51</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:51</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,6 +1149,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1211,10 +1168,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>116929266</v>
+        <v>115703646</v>
       </c>
       <c r="B7" t="n">
-        <v>57676</v>
+        <v>57247</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1222,42 +1179,49 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100110</v>
+        <v>100038</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Holmensbäcken, Holmensbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>631244</v>
+        <v>631093</v>
       </c>
       <c r="R7" t="n">
-        <v>6928065</v>
+        <v>6927953</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1281,12 +1245,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,12 +1275,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Mattias Edman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Mattias Edman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1316,11 +1290,11 @@
         <v>116930260</v>
       </c>
       <c r="B8" t="n">
-        <v>57681</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1413,11 +1387,11 @@
         <v>131110701</v>
       </c>
       <c r="B9" t="n">
-        <v>57895</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1519,10 +1493,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131110722</v>
+        <v>116929266</v>
       </c>
       <c r="B10" t="n">
-        <v>80269</v>
+        <v>57945</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1530,40 +1504,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>100110</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Myckeläng, Mpd</t>
+          <t>Holmensbäcken, Holmensbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>631117</v>
+        <v>631244</v>
       </c>
       <c r="R10" t="n">
-        <v>6928040</v>
+        <v>6928065</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1587,12 +1563,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1601,19 +1577,18 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mattias Edman</t>
+          <t>Mikael Gudrunsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mattias Edman</t>
+          <t>Mikael Gudrunsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 11288-2024 artfynd.xlsx
+++ b/artfynd/A 11288-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115639618</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115640415</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115640666</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115702027</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131110722</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115703646</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116930260</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1490,6 +1530,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131110701</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1592,8 +1637,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116929266</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>